--- a/generalDesign_documentation/powerCalculations.xlsx
+++ b/generalDesign_documentation/powerCalculations.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Parry\Documents\GitHub\Vital-link-hardware\generalDesign_documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5691BE37-CD46-4918-B804-6F437838EE0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{915D0CE1-555E-40EB-8636-AF695946CC3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1845" yWindow="0" windowWidth="23940" windowHeight="12435" xr2:uid="{2C8B698D-5FDE-48B6-9C15-0E27123BF32D}"/>
+    <workbookView xWindow="31680" yWindow="1035" windowWidth="23940" windowHeight="12435" xr2:uid="{2C8B698D-5FDE-48B6-9C15-0E27123BF32D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,6 +33,23 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+  <si>
+    <t>V_bat Max(V)</t>
+  </si>
+  <si>
+    <t>V_bat Min(V)</t>
+  </si>
+  <si>
+    <t>LDO V_BAT-&gt;3V3 (300mA MAX)</t>
+  </si>
+  <si>
+    <t>Vdo( Dropout Voltage)</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -402,9 +419,42 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF26992E-C83A-430F-AA22-AF7591923049}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="31.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6">
+        <v>0.3</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>